--- a/Lista_Invitados_Boda.xlsx
+++ b/Lista_Invitados_Boda.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\invitacion-katherin-alejandro\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -153,9 +153,6 @@
     <t>OLVIN ELVIR Y ESPOSA</t>
   </si>
   <si>
-    <t>CISTIAN ELVIR Y ESPOSA</t>
-  </si>
-  <si>
     <t>DENIS ARGUETA Y FAMILIA</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>NELDA GARCÍA Y FAMILIA</t>
   </si>
   <si>
-    <t>LOURDES ALVARADO</t>
-  </si>
-  <si>
     <t>LUIS ARTURO GARCÍA</t>
   </si>
   <si>
@@ -445,6 +439,12 @@
   </si>
   <si>
     <t>GERSON RODRIGUEZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>CRISTIAN ELVIR Y ESPOSA</t>
+  </si>
+  <si>
+    <t>JUAN VALLECILLO Y ESPOSA</t>
   </si>
 </sst>
 </file>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1283,7 +1283,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1294,7 +1294,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -1305,7 +1305,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1316,7 +1316,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1327,7 +1327,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1338,7 +1338,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -1349,7 +1349,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -1360,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -1371,7 +1371,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1382,7 +1382,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1404,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1426,7 +1426,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1437,7 +1437,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -1448,7 +1448,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -1459,7 +1459,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -1470,7 +1470,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -1481,7 +1481,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1492,7 +1492,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1503,7 +1503,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -1514,7 +1514,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -1525,7 +1525,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -1536,7 +1536,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -1547,7 +1547,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -1558,7 +1558,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -1569,7 +1569,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -1580,7 +1580,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -1591,7 +1591,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -1602,7 +1602,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1613,7 +1613,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -1624,7 +1624,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -1635,7 +1635,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -1646,7 +1646,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -1657,7 +1657,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -1668,7 +1668,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -1679,7 +1679,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -1690,7 +1690,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -1701,7 +1701,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C83">
         <v>4</v>
@@ -1712,7 +1712,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -1723,7 +1723,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -1734,7 +1734,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C86">
         <v>3</v>
@@ -1745,7 +1745,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C87">
         <v>3</v>
@@ -1756,7 +1756,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -1767,7 +1767,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -1778,7 +1778,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -1789,7 +1789,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -1800,7 +1800,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -1811,7 +1811,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C93">
         <v>3</v>
@@ -1822,7 +1822,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C94">
         <v>3</v>
@@ -1833,7 +1833,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -1844,7 +1844,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -1855,7 +1855,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -1866,7 +1866,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -1877,7 +1877,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C99">
         <v>3</v>
@@ -1888,7 +1888,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -1910,7 +1910,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -1921,7 +1921,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -1932,7 +1932,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -1954,7 +1954,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -1965,7 +1965,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -1976,7 +1976,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C108">
         <v>6</v>
@@ -1987,7 +1987,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C109">
         <v>3</v>
@@ -1998,7 +1998,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -2009,7 +2009,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -2020,7 +2020,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -2031,7 +2031,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -2042,7 +2042,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -2053,7 +2053,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -2064,7 +2064,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -2075,7 +2075,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -2086,7 +2086,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -2108,7 +2108,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -2119,7 +2119,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -2130,7 +2130,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -2141,7 +2141,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -2152,7 +2152,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -2163,7 +2163,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -2174,7 +2174,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -2185,7 +2185,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -2196,7 +2196,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -2207,7 +2207,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -2218,7 +2218,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -2229,7 +2229,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C132">
         <v>3</v>
@@ -2251,7 +2251,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -2262,7 +2262,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -2273,7 +2273,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -2284,7 +2284,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -2295,7 +2295,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -2317,7 +2317,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -2328,7 +2328,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C140">
         <v>2</v>

--- a/Lista_Invitados_Boda.xlsx
+++ b/Lista_Invitados_Boda.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Invitados" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invitados!$A$1:$C$140</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="142">
   <si>
     <t>No.</t>
   </si>
@@ -258,9 +258,6 @@
     <t>UBALDO FLORES</t>
   </si>
   <si>
-    <t>FREDAL ANTONIO PAZY ESPOSA</t>
-  </si>
-  <si>
     <t>LUIS ROBERTO PAZ Y FAMILIA</t>
   </si>
   <si>
@@ -300,9 +297,6 @@
     <t>NESTOR RIVAS Y ESPOSA</t>
   </si>
   <si>
-    <t>ERWIN SALINAS Y ESPOSA</t>
-  </si>
-  <si>
     <t>BAYRON RUIZ Y ESPOSA</t>
   </si>
   <si>
@@ -429,15 +423,9 @@
     <t>SIRLEY SUAZO</t>
   </si>
   <si>
-    <t>NARBEL FUNEZ</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL CHAVARRIA Y ESPOSA</t>
   </si>
   <si>
-    <t>MAURO VALLADARES Y ESPOSA</t>
-  </si>
-  <si>
     <t>GERSON RODRIGUEZ Y ESPOSA</t>
   </si>
   <si>
@@ -445,6 +433,21 @@
   </si>
   <si>
     <t>JUAN VALLECILLO Y ESPOSA</t>
+  </si>
+  <si>
+    <t>MAURO ERNESTO VALLADARES Y ESPOSA</t>
+  </si>
+  <si>
+    <t>NORBEL FUNEZ</t>
+  </si>
+  <si>
+    <t>HERWIN SALINAS Y ESPOSA</t>
+  </si>
+  <si>
+    <t>FREDA ANTONIO PAZ Y ESPOSA</t>
+  </si>
+  <si>
+    <t>NICOLL PORTILLO</t>
   </si>
 </sst>
 </file>
@@ -787,7 +790,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -810,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -876,7 +879,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1283,7 +1286,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1415,7 +1418,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1690,7 +1693,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -1701,7 +1704,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C83">
         <v>4</v>
@@ -1712,7 +1715,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -1723,7 +1726,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -1734,7 +1737,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86">
         <v>3</v>
@@ -1745,7 +1748,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87">
         <v>3</v>
@@ -1756,7 +1759,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -1767,7 +1770,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -1778,7 +1781,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -1789,7 +1792,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -1800,7 +1803,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -1811,7 +1814,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93">
         <v>3</v>
@@ -1822,7 +1825,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94">
         <v>3</v>
@@ -1833,7 +1836,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -1844,7 +1847,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -1855,7 +1858,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -1866,7 +1869,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -1877,7 +1880,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C99">
         <v>3</v>
@@ -1888,7 +1891,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -1899,7 +1902,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -1910,7 +1913,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -1921,7 +1924,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -1932,7 +1935,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -1943,7 +1946,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -1954,7 +1957,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -1965,7 +1968,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -1976,7 +1979,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C108">
         <v>6</v>
@@ -1987,7 +1990,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C109">
         <v>3</v>
@@ -1998,7 +2001,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -2009,7 +2012,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -2020,7 +2023,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -2031,7 +2034,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -2042,7 +2045,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -2053,7 +2056,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -2064,7 +2067,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -2075,7 +2078,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -2086,7 +2089,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -2097,7 +2100,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -2108,7 +2111,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -2119,7 +2122,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -2130,7 +2133,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -2141,7 +2144,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -2152,7 +2155,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -2163,7 +2166,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -2174,7 +2177,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -2185,7 +2188,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -2207,7 +2210,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -2218,7 +2221,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -2229,7 +2232,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -2240,7 +2243,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C132">
         <v>3</v>
@@ -2251,7 +2254,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -2262,7 +2265,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -2273,7 +2276,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -2284,7 +2287,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -2295,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -2306,7 +2309,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -2317,7 +2320,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -2328,14 +2331,25 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C140">
         <v>2</v>
       </c>
     </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>141</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C134"/>
+  <autoFilter ref="A1:C140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
